--- a/artfynd/A 38556-2026 artfynd.xlsx
+++ b/artfynd/A 38556-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136347709</v>
       </c>
       <c r="B2" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136347710</v>
       </c>
       <c r="B3" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136347663</v>
       </c>
       <c r="B4" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38556-2026 artfynd.xlsx
+++ b/artfynd/A 38556-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136347709</v>
       </c>
       <c r="B2" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136347710</v>
       </c>
       <c r="B3" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136347663</v>
       </c>
       <c r="B4" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38556-2026 artfynd.xlsx
+++ b/artfynd/A 38556-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136347709</v>
       </c>
       <c r="B2" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136347710</v>
       </c>
       <c r="B3" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136347663</v>
       </c>
       <c r="B4" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38556-2026 artfynd.xlsx
+++ b/artfynd/A 38556-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136347709</v>
       </c>
       <c r="B2" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136347710</v>
       </c>
       <c r="B3" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136347663</v>
       </c>
       <c r="B4" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
